--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="466">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -1852,6 +1852,668 @@
   </si>
   <si>
     <t xml:space="preserve">potion_farris</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">into_darkness5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">editPlaylist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">これが「淀み」か。
+黒く濁っていて…覗いているだけで呑み込まれそうだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So this is the "Pool".
+Black and murky... just looking into it feels like it might swallow me whole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気味の悪い場所です。イスシズルの用事を済ませて、早々に立ち去りましょう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a dreadful place. Let’s finish Issizzle’s errand and leave at once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その意見には全く賛成だよ。
+この「淀み」に一滴の雫を垂らす…簡単な仕事だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I cannot agree more.
+Just dripping a single drop into this "Pool". A simple task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">では、#pc、どちらの瓶を使う？ イスシズルに渡されたこの得体の知れない瓶か、ファリスさん特製の洗…聖水か。
+（…おい、#pc、聞こえるか？）
+（ファリスさんもついて来てしまったが、安心しろ。お前がどちらを選んでも、ばれないように上手くやってやる。お前の決断を尊重するよ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So, #pc, which bottle will you use? This eerie one Issizzle gave us, or Lady Farris’s... holy water?
+(...#pc, you hear me?)
+(Lady Farris ended up coming along, but don’t worry. Whichever one you choose, I’ll make sure she never finds out. I’ll respect your decision.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イスシズルの瓶を使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Issizzle’s bottle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスの瓶を使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Farris’s bottle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…イスシズルの瓶で間違いないか？
+とても穢れた匂いだ。この一滴は、やがて邪悪なるものを育むことだろう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...This Issizzle’s bottle, yes?
+It reeks of corruption. This single drop will no doubt nurture something wicked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いいえ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ファリスさんのこの瓶で間違いないか？
+とても…いい匂いだ。この一滴が何をもたらすのか、検討もつかないよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...This Lady Farris’s bottle, yes?
+It smells... wonderful. I can’t even guess what this one drop will bring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water_choice2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">setFlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farris_water,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">よし。では、私がこの瓶の雫を一滴、「淀み」に垂らしてこよう。
+いや、#pc、これぐらいはさせてくれ。お前だけに重荷を背負わすわけにはいかないさ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All right. I’ll go drip a single drop from this bottle into the "Pool".
+No, #pc, let me do at least this much. I can’t let you bear all the burdens alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…この一滴で世界の命運が変わるかもしれない、そう思うと息が詰まるようだ。
+それにこの床がまた…妙にヌメヌメしていて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Thinking that a single drop might change the fate of the world... it’s almost suffocating.
+And this floor, it’s really slimy and...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あ゛っ゛！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agh!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potion_sorin,-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potion_farris,-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お、落ち着け、私なら大丈夫だ！
+…ふぅ、全身びしょ濡れになってしまって気持ち悪いが、この「淀み」がそんなに深くなくて助かった。
+ハッ…瓶は…2本ともどこにいった？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-Calm down, I’m fine!
+...Whew. I’m soaked from head to toe. It feels awful, but at least the "Pool" wasn’t that deep.
+Wait... where did both bottles go?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ロイテル様…！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Lord Loytel...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスさん、落ち着いて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lady Farris, calm down...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">後ろ、後ろです！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind — behind you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bossText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">az</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・シェ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヌル・アザ゛ルゥ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ル……ネ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">イフ・ダロゥン……サ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラ・クン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">アグラ… 
+…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・シェ……ル゛ェ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ノル・シャ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラグン……ハ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ザ… ！！</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...RU=VA SHE=NUR AZZALUU=RU... NE=IF DALOON... SA=RA KUN=AGRA...
+...RU=VA SHE... L’E=NOR SHA=RAGUN... HA=ZA...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">な…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wh—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何を言っているか全くわからないが、相当怒っているようだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have no idea what it’s saying, but it sounds furious.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…ル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ヴァ・ザ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ノゥ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ル゛ェ……アグ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">シェ…アグシェネ゛…イ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ドラ……シャ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ラ・フン…… ！！</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...RU=VA ZA=NOO=LE... AG=SHE... AGSHENE... I=DRA... SHA=LA FUN...!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おお…不浄なる者アズラシズル…かつて地上を恐怖に陥れ、神々に封印されし邪神です…！</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">The Unpure, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">Azrasizzle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">... the ancient evil god once sealed by the gods themselves...!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…これが「淀み」の正体、いずれ芽吹く災いの種か。ちょうどいい、そんなものは、今ここで刈り取ってやる。
+ふっ、流石の邪神も、そのフレッシュな香りでは思う存分に力を発揮できまい。
+さあ、#pc、後は任せたぞ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...So this is the true nature of the "Pool". A seed of calamity waiting to sprout. It should end here and now.
+Heh... even an evil god probably can’t unleash its full strength with such a fresh scent clinging to it.
+Go on, #pc. I leave the rest to you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_az3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">into_darkness6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">alphaIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おお、やったな、#pc！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well done, #pc!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お見事です、#player様。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splendid work, #player.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この化け物が出てきた時は、もうダメかと思ったが…まあ、 終わってみればなんとかなるものだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When that monster showed up, I thought we were finished... but in the end, things have a way of working out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イスシズルめ…とんでもない奴だ。遠い未来とはいえ、自らの野望のためにこんなものを世に解き放とうと考えていたとは。
+しかし、困ったことになったな。これでは奴との約束が果たせないぞ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issizzle... that wretch. Even if the calamity lies far in the future, I can’t believe he’d unleash something like this for the sake of his ambition.
+But this is troubling. Now we can’t keep our promise to him.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私たちは何も見なかったし、ここでは何も起きなかった…いいですね、ロイテル様？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We saw nothing, and nothing happened here... Isn’t that right, Lord Loytel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ああ。奴が簡単に信じるとは思い難いが、そう話すしかないだろう。
+よし、ひとまずは拠点に帰って、イスシズルを待つとしよう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Yes. I doubt he’ll believe it so easily, but that’s all we can say.
+All right. Let’s return to the base and wait for Issizzle.</t>
   </si>
 </sst>
 </file>
@@ -1862,7 +2524,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1955,6 +2617,18 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2004,7 +2678,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2075,6 +2749,14 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2275,7 +2957,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IX329"/>
+  <dimension ref="A1:IX400"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
@@ -2331,7 +3013,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="1" t="n">
         <f aca="false">MAX(I4:I1048576)</f>
-        <v>193</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7404,9 +8086,769 @@
         <v>76</v>
       </c>
     </row>
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F332" s="16"/>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E333" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F333" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="J333" s="6"/>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F334" s="16"/>
+    </row>
+    <row r="335" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F335" s="16"/>
+      <c r="G335" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I335" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="J335" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="K335" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F336" s="16"/>
+      <c r="G336" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I336" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="J336" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F337" s="16"/>
+      <c r="J337" s="7"/>
+      <c r="K337" s="4"/>
+    </row>
+    <row r="338" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F338" s="16"/>
+      <c r="G338" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I338" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="J338" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="K338" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F339" s="16"/>
+      <c r="J339" s="7"/>
+      <c r="K339" s="6"/>
+    </row>
+    <row r="340" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F340" s="16"/>
+      <c r="G340" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I340" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="J340" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="K340" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B341" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F341" s="16"/>
+      <c r="I341" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="J341" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B342" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F342" s="16"/>
+      <c r="I342" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="J342" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F343" s="16"/>
+      <c r="J343" s="7"/>
+      <c r="K343" s="6"/>
+    </row>
+    <row r="344" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F344" s="16"/>
+      <c r="G344" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I344" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="J344" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="K344" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B345" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F345" s="16"/>
+      <c r="I345" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="J345" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="K345" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B346" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F346" s="16"/>
+      <c r="I346" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="J346" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="K346" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F347" s="16"/>
+      <c r="J347" s="7"/>
+      <c r="K347" s="6"/>
+    </row>
+    <row r="348" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F348" s="16"/>
+      <c r="G348" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I348" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="J348" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="K348" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B349" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F349" s="16"/>
+      <c r="I349" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="J349" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="K349" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B350" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F350" s="16"/>
+      <c r="I350" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="J350" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="K350" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F351" s="16"/>
+      <c r="J351" s="7"/>
+      <c r="K351" s="6"/>
+    </row>
+    <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F352" s="16"/>
+      <c r="J352" s="7"/>
+      <c r="K352" s="6"/>
+    </row>
+    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E353" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J353" s="7"/>
+      <c r="K353" s="6"/>
+    </row>
+    <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F354" s="16"/>
+      <c r="J354" s="7"/>
+      <c r="K354" s="6"/>
+    </row>
+    <row r="355" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F355" s="16"/>
+      <c r="G355" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I355" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="J355" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="K355" s="6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F356" s="16"/>
+      <c r="G356" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I356" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="J356" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="K356" s="6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E357" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F357" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="J357" s="7"/>
+      <c r="K357" s="6"/>
+    </row>
+    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F358" s="16"/>
+      <c r="G358" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I358" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="J358" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="K358" s="6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F359" s="16"/>
+      <c r="J359" s="7"/>
+      <c r="K359" s="6"/>
+    </row>
+    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F360" s="16"/>
+      <c r="G360" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I360" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="J360" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K360" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F361" s="16"/>
+      <c r="G361" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I361" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="J361" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K361" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E362" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F362" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="J362" s="7"/>
+      <c r="K362" s="6"/>
+    </row>
+    <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E363" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F363" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="J363" s="7"/>
+      <c r="K363" s="6"/>
+    </row>
+    <row r="364" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F364" s="16"/>
+      <c r="G364" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I364" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="J364" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="K364" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F365" s="16"/>
+      <c r="G365" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I365" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="J365" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="K365" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F366" s="16"/>
+      <c r="G366" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I366" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="J366" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="K366" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F367" s="16"/>
+      <c r="G367" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I367" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="J367" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="K367" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F368" s="16"/>
+      <c r="J368" s="7"/>
+      <c r="K368" s="6"/>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E369" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F369" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="J369" s="6"/>
+    </row>
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F370" s="16"/>
+      <c r="J370" s="6"/>
+    </row>
+    <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F371" s="16"/>
+      <c r="J371" s="3"/>
+      <c r="K371" s="4"/>
+    </row>
+    <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E372" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F372" s="16"/>
+      <c r="J372" s="3"/>
+      <c r="K372" s="4"/>
+    </row>
+    <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E373" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F373" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J373" s="3"/>
+      <c r="K373" s="4"/>
+    </row>
+    <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E374" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F374" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="J374" s="3"/>
+      <c r="K374" s="4"/>
+    </row>
+    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E375" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F375" s="16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F376" s="16"/>
+      <c r="G376" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I376" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="J376" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="K376" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F377" s="16"/>
+      <c r="G377" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I377" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="J377" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="K377" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F378" s="16"/>
+      <c r="G378" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I378" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="J378" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="K378" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F379" s="16"/>
+      <c r="G379" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I379" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="J379" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="K379" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="23.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F380" s="16"/>
+      <c r="G380" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I380" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="J380" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="K380" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F381" s="16"/>
+      <c r="G381" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I381" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="J381" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="K381" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E382" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F382" s="16" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E383" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F383" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E384" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F384" s="16" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E385" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F385" s="16"/>
+    </row>
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F386" s="16"/>
+    </row>
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F388" s="16"/>
+    </row>
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E389" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F389" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E390" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="F390" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G390" s="6"/>
+      <c r="J390" s="6"/>
+    </row>
+    <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G392" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I392" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="J392" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="K392" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F393" s="16"/>
+      <c r="G393" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I393" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="J393" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="K393" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F394" s="16"/>
+      <c r="G394" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I394" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="J394" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="K394" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F395" s="16"/>
+      <c r="G395" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I395" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="J395" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="K395" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F396" s="16"/>
+      <c r="G396" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I396" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="J396" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="K396" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F397" s="16"/>
+      <c r="G397" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I397" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="J397" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="K397" s="6" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F398" s="16"/>
+      <c r="J398" s="6"/>
+    </row>
+    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E399" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F399" s="16"/>
+    </row>
+    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F400" s="16"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I4:I1048576">
+  <conditionalFormatting sqref="I4:I374 I384:I1048576">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I383 I375:I381">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I382">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="522">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -2514,6 +2514,276 @@
   <si>
     <t xml:space="preserve">...Yes. I doubt he’ll believe it so easily, but that’s all we can say.
 All right. Let’s return to the base and wait for Issizzle.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">into_darkness7</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bg_road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ケトル…ちょっといい？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kettle... can I talk to you?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どうしたんだい、クルイツゥア？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, Quruitzia?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さっきね、見たことのない黒ローブの男の子が、私とコルゴンをじっと見ていたの。だから、話しかけようとしたら、デミタスがすごい剣幕で割って入って来て、その子と口論を始めて…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlier... I saw a boy in a black robe I’d never seen before, just staring at me and Corgon. So I tried to talk to him, but Demitas barged in all furious and started arguing with him...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…そうか、そろそろ現れる頃だと思っていたよ。
+その黒ローブの子はソリン、イスシズルの人間の姿だ。デミタスと彼とは、過去にちょっとした因縁があってね。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I see... I thought he’d be showing up about now.
+The boy in black is Sorin—Issizzle’s human form. Demitas and he have... a bit of history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あの子が…イスシズル？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That boy... is Issizzle?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恐れることは何もない、クルイツゥア。私たちは死者の洞窟で彼との約束を果たしたんだから。
+そうだね、ロイテル？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There’s nothing to fear, Quruitzia. We kept our promise to him in the Crypt of the Damned.
+Isn’t that right, Loytel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…その、ケトル…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Well, Kettle...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何かな？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">い、いや、確かにもう危険は去ったはずだが…念のために聞かせてくれ。イスシズルを怒らせると、一体どうなるんだ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-nothing... I’m sure the danger has passed, but just in case, what happens if we make Issizzle angry?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その気になれば、国ひとつ簡単に滅ぼす力を持った魔術師だ。彼は、この時代で私たちが最も怒らせたくない相手の一人だろうね。
+でも、心配には及ばないさ、ロイテル。なぜなら、ふふ、もし君が「彼を怒らせることでもしていた」のなら、君はとっくに地面の下で眠っているだろうからね。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is a sorcerer powerful enough to wipe out an entire kingdom. In this age, he is certainly one of the last people we want to provoke.
+But don’t worry, Loytel. Because &lt;b&gt;if you’d done anything to anger him&lt;/b&gt;, you’d already be sleeping under the ground, hehe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…は…ははは、そうか…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...H-hahaha... I see...!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ひそひそ）ファリスさん、「淀み」で起こったことは、絶対に奴には黙っていよう。ケトルにだって、もうだいぶ怪しまれているぞ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(whisper) Lady Farris—whatever happened in the "Pool", we must absolutely keep it from him. Even Kettle is already growing suspicious.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ひそひそ）はい、ロイテル様…唄にできないのは心残りですが、今回ばかりは止むを得ません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(whisper) Yes, Lord Loytel... It’s a shame we can’t turn it into a song, but it can’t be helped this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…さて、デミタスもそろそろ鎮まっている頃だろう。私たちも話を聞きに行こう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...All right. Demitas has probably cooled off by now. Let’s go hear what he has to say.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…では、約束は無事果たされたと考えて良いのですね？
+なに、ただの確認ですよ。「淀み」への干渉は、僕にもすぐ感じ取ることができました。ただ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Then we may assume the promise was fulfilled without incident?
+No, it’s just a confirmation. I sensed the interference with the "Pool" at once. However...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ただ…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ただ、その時を境に、僕の魔力の一部が失われたのです。厳密に言えば、僕は「イスシズル」の不死の肉体を失ってしまった。
+フッ、もちろん、それはつまり、再び「淀み」が動き出したという喜ばしい確証でもあるのです。
+心配には及びませんよ。「淀み」でかの者の力が増せば、僕の魔力もまた戻って来るでしょう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From that moment on, a portion of my magic was lost. To be precise, I lost Issizzle’s immortal body.
+Heh, but that is, in itself, a most welcome proof that the "Pool" has begun to stir again.
+There is no need for concern. As that being’s power grows within the "Pool", my own magic will return as well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔力が失われただって？　それは良かっ…いや、災難だったな！
+では、もうコルゴンやクルイツゥアに身の危険はないということか。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You lost some of your power? That’s wonderf— no, that’s terrible!
+Then does that mean Corgon and Quruitzia are no longer in danger?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…師よ、ここにいる愚か者にも理解できるよう、後でよく教えてやるといいでしょう。魔術師にとって言葉がどれほど重いものかを。
+僕は約束を守ると決めています。たとえ今すぐにでも、その男が気に触ったという理由だけで、この場を惨状に変えられる魔力が僕に残っているとしても、です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Master, you would do well to explain this properly later, so that even the fool standing here may understand how heavy words are to a mage. 
+I have decided to keep my promise, even if I still possess the magic to turn this place into a scene of devastation at this very moment, for no reason other than that fool displeasing me.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…フッ、まあ構いません。どのみち、この場に居る者の大半とは、もう二度と顔を合わせることもないのです。
+竜の子と魔女という珍しいものが見れた上に、古き友とも実に和やかな交流ができたのですから、わざわざ足を運んだだけの甲斐はあったというものです。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">では、師よ。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...No matter. In any case, I doubt I shall ever meet most of those present here again.
+To have seen such curiosities as a dragon child and a witch, and to share so cordial an exchange with an old friend, I suppose it was worth the trouble of coming.
+Now then, Master.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ソリン、その身体であの古城に帰る気かい？
+悪気はないけど、この前訪れた時は、とても「人間」がくつろげる場所だとは思えなかったよ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sorin, are you really going back to that old castle in your...current body?
+No offense, but last time I visited your castle, it hardly felt like a place a "human" could relax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふふ、そんなに怖い顔をしないでくれ。言い直すよ。
+君の魔力が戻るまで、ここで暮らしてみないか、ソリン？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hehe, don’t make such a frightening face. Let me put it another way.
+Why not live here with us until your magic returns, Sorin? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">（スーッ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Takes a deep breath) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">それは…意外な申し出です、師よ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That is... an unexpected offer, Master.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">…そして、僕にとって好都合とも言えるでしょう。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">竜の子と魔女の邂逅が意味するもの、 運命の糸に引かれた冒険者、そして何よりも師よ、魔石の秘密を知ってから、あなたという存在そのものが、僕の好奇心を離さないのです。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">...And one that is quite convenient for me.
+The meaning behind the meeting of the dragon child and the witch, the adventurer drawn by the threads of fate, and above all, Master—ever since I learned the secret of the magic stone, your very existence has refused to let go of my curiosity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">もちろん、ただで宿を得るつもりはありません。
+僕がここに留まる見返りとして、何をお望みですか？ 失われし上古の魔法書、不老不死の薬、あるいは、休むことなく働き続ける死者の軍団でも作ってみせましょうか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of course, I have no intention of taking lodging for free.
+What would you desire in return? A lost grimoire of the ancient age, an elixir of immortality, or perhaps an army of the dead that never tires of labor?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">見返りか、そうだね、コルゴンがボロボロにした鍋の修理ぐらいは頼ませてもらうとするよ。
+だけど、まずは君の滞在を歓迎しよう。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">そしてソリン、まだ私を師と呼ぶのなら、覚えておくといい。君も…私も、この世界にはまだ多くの学ぶべきことが残っているんだ、どれだけ長生きだろうともね。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Well, I suppose I’ll at least ask you to repair the pots Corgon battered to pieces.
+But regardless, I welcome your stay here. 
+And Sorin, if you still call me your Master, remember. We still have much to learn from this world, however long our lives may be. </t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2794,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2629,6 +2899,12 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2678,7 +2954,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2751,11 +3027,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2957,7 +3253,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IX400"/>
+  <dimension ref="A1:IX451"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
@@ -2968,7 +3264,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="62.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
@@ -3013,7 +3309,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="1" t="n">
         <f aca="false">MAX(I4:I1048576)</f>
-        <v>235</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8385,7 +8681,7 @@
       <c r="I356" s="1" t="n">
         <v>213</v>
       </c>
-      <c r="J356" s="18" t="s">
+      <c r="J356" s="7" t="s">
         <v>417</v>
       </c>
       <c r="K356" s="6" t="s">
@@ -8644,7 +8940,7 @@
       <c r="I379" s="1" t="n">
         <v>224</v>
       </c>
-      <c r="J379" s="19" t="s">
+      <c r="J379" s="18" t="s">
         <v>444</v>
       </c>
       <c r="K379" s="6" t="s">
@@ -8659,7 +8955,7 @@
       <c r="I380" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="J380" s="19" t="s">
+      <c r="J380" s="18" t="s">
         <v>446</v>
       </c>
       <c r="K380" s="6" t="s">
@@ -8775,7 +9071,7 @@
       <c r="I394" s="1" t="n">
         <v>232</v>
       </c>
-      <c r="J394" s="19" t="s">
+      <c r="J394" s="18" t="s">
         <v>458</v>
       </c>
       <c r="K394" s="6" t="s">
@@ -8790,7 +9086,7 @@
       <c r="I395" s="1" t="n">
         <v>233</v>
       </c>
-      <c r="J395" s="19" t="s">
+      <c r="J395" s="18" t="s">
         <v>460</v>
       </c>
       <c r="K395" s="6" t="s">
@@ -8839,6 +9135,603 @@
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F400" s="16"/>
+    </row>
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F401" s="16"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E403" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F403" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G403" s="6"/>
+      <c r="J403" s="6"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E404" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F404" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E405" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F405" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="J405" s="7"/>
+      <c r="K405" s="6"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E406" s="6"/>
+      <c r="F406" s="10"/>
+      <c r="J406" s="6"/>
+      <c r="K406" s="6"/>
+    </row>
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E407" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F407" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="J407" s="6"/>
+      <c r="K407" s="6"/>
+    </row>
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E408" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F408" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J408" s="18"/>
+      <c r="K408" s="6"/>
+    </row>
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J409" s="18"/>
+      <c r="K409" s="6"/>
+    </row>
+    <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G410" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I410" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="J410" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="K410" s="20" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G411" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I411" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="J411" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="K411" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G412" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I412" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="J412" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="K412" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G413" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I413" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="J413" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="K413" s="20" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G414" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I414" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="J414" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="K414" s="20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G415" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I415" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="J415" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="K415" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G416" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I416" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="J416" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="K416" s="20" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G417" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I417" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="J417" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="K417" s="20" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G418" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I418" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="J418" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="K418" s="20" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G419" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I419" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="J419" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="K419" s="20" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G420" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I420" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="J420" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="K420" s="20" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G421" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I421" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="J421" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="K421" s="22" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G422" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I422" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="J422" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="K422" s="20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G423" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I423" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="J423" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="K423" s="20" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J424" s="7"/>
+      <c r="K424" s="20"/>
+    </row>
+    <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E425" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F425" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J425" s="7"/>
+      <c r="K425" s="20"/>
+    </row>
+    <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E426" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F426" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J426" s="7"/>
+      <c r="K426" s="20"/>
+    </row>
+    <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E427" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F427" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G427" s="6"/>
+      <c r="J427" s="7"/>
+      <c r="K427" s="20"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J428" s="18"/>
+      <c r="K428" s="20"/>
+    </row>
+    <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F429" s="16"/>
+      <c r="G429" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I429" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="J429" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K429" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F430" s="16"/>
+      <c r="G430" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I430" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="J430" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="K430" s="20" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F431" s="16"/>
+      <c r="G431" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I431" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="J431" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="K431" s="22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F432" s="16"/>
+      <c r="G432" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I432" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="J432" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="K432" s="20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F433" s="16"/>
+      <c r="G433" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I433" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="J433" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K433" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F434" s="16"/>
+      <c r="G434" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I434" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="J434" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="K434" s="20" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F435" s="16"/>
+      <c r="G435" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I435" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="J435" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="K435" s="20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F436" s="16"/>
+      <c r="G436" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I436" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="J436" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="K436" s="20" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F437" s="16"/>
+      <c r="G437" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I437" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="J437" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="K437" s="20" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F438" s="16"/>
+      <c r="G438" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I438" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="J438" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K438" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F439" s="16"/>
+      <c r="G439" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I439" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="J439" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="K439" s="20" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F440" s="16"/>
+      <c r="G440" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I440" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="J440" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="K440" s="20" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F441" s="16"/>
+      <c r="G441" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I441" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="J441" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="K441" s="20" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F442" s="16"/>
+      <c r="G442" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I442" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="J442" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K442" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F443" s="16"/>
+      <c r="G443" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I443" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="J443" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="K443" s="20" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F444" s="16"/>
+      <c r="G444" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I444" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="J444" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="K444" s="20" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F445" s="16"/>
+      <c r="G445" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I445" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="J445" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="K445" s="20" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="76.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F446" s="16"/>
+      <c r="G446" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I446" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="J446" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="K446" s="20" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F447" s="16"/>
+      <c r="J447" s="7"/>
+      <c r="K447" s="6"/>
+    </row>
+    <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F448" s="16"/>
+      <c r="J448" s="7"/>
+      <c r="K448" s="6"/>
+    </row>
+    <row r="449" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E449" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F449" s="16"/>
+      <c r="J449" s="6"/>
+      <c r="K449" s="6"/>
+    </row>
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F450" s="16"/>
+      <c r="J450" s="6"/>
+    </row>
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E451" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F451" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I374 I384:I1048576">

--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -2664,7 +2664,7 @@
   </si>
   <si>
     <t xml:space="preserve">…師よ、ここにいる愚か者にも理解できるよう、後でよく教えてやるといいでしょう。魔術師にとって言葉がどれほど重いものかを。
-僕は約束を守ると決めています。たとえ今すぐにでも、その男が気に触ったという理由だけで、この場を惨状に変えられる魔力が僕に残っているとしても、です。</t>
+僕は約束を守ると決めています。たとえ今すぐにでも、その男が気に障ったという理由だけで、この場を惨状に変えられる魔力が僕に残っているとしても、です。</t>
   </si>
   <si>
     <t xml:space="preserve">…Master, you would do well to explain this properly later, so that even the fool standing here may understand how heavy words are to a mage. 
@@ -2954,7 +2954,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3028,26 +3028,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3488,7 +3468,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="1" t="n">
         <v>22</v>
       </c>
@@ -3499,7 +3479,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="1" t="n">
         <v>23</v>
       </c>
@@ -3621,7 +3601,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="1" t="n">
         <v>16</v>
       </c>
@@ -4089,7 +4069,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G84" s="1" t="s">
         <v>88</v>
       </c>
@@ -4419,7 +4399,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="6" t="s">
         <v>88</v>
       </c>
@@ -4433,7 +4413,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="6" t="s">
         <v>88</v>
       </c>
@@ -4495,7 +4475,7 @@
       <c r="J119" s="7"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E120" s="6"/>
       <c r="F120" s="10"/>
       <c r="G120" s="6" t="s">
@@ -4836,7 +4816,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G146" s="6" t="s">
         <v>47</v>
       </c>
@@ -5620,7 +5600,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
@@ -6703,7 +6683,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
       <c r="G224" s="6" t="s">
@@ -8132,7 +8112,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G306" s="6" t="s">
         <v>47</v>
       </c>
@@ -8400,7 +8380,7 @@
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F334" s="16"/>
     </row>
-    <row r="335" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F335" s="16"/>
       <c r="G335" s="1" t="s">
         <v>47</v>
@@ -8458,7 +8438,7 @@
       <c r="J339" s="7"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F340" s="16"/>
       <c r="G340" s="1" t="s">
         <v>47</v>
@@ -8658,7 +8638,7 @@
       <c r="J354" s="7"/>
       <c r="K354" s="6"/>
     </row>
-    <row r="355" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F355" s="16"/>
       <c r="G355" s="1" t="s">
         <v>47</v>
@@ -9078,7 +9058,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F395" s="16"/>
       <c r="G395" s="1" t="s">
         <v>47</v>
@@ -9108,7 +9088,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F397" s="16"/>
       <c r="G397" s="1" t="s">
         <v>47</v>
@@ -9207,10 +9187,10 @@
       <c r="I410" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="J410" s="19" t="s">
+      <c r="J410" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="K410" s="20" t="s">
+      <c r="K410" s="6" t="s">
         <v>469</v>
       </c>
     </row>
@@ -9224,7 +9204,7 @@
       <c r="J411" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="K411" s="20" t="s">
+      <c r="K411" s="6" t="s">
         <v>471</v>
       </c>
     </row>
@@ -9238,7 +9218,7 @@
       <c r="J412" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="K412" s="20" t="s">
+      <c r="K412" s="6" t="s">
         <v>473</v>
       </c>
     </row>
@@ -9252,7 +9232,7 @@
       <c r="J413" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="K413" s="20" t="s">
+      <c r="K413" s="6" t="s">
         <v>475</v>
       </c>
     </row>
@@ -9263,10 +9243,10 @@
       <c r="I414" s="1" t="n">
         <v>254</v>
       </c>
-      <c r="J414" s="19" t="s">
+      <c r="J414" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="K414" s="20" t="s">
+      <c r="K414" s="6" t="s">
         <v>477</v>
       </c>
     </row>
@@ -9280,7 +9260,7 @@
       <c r="J415" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="K415" s="20" t="s">
+      <c r="K415" s="6" t="s">
         <v>479</v>
       </c>
     </row>
@@ -9294,7 +9274,7 @@
       <c r="J416" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="K416" s="20" t="s">
+      <c r="K416" s="6" t="s">
         <v>481</v>
       </c>
     </row>
@@ -9308,7 +9288,7 @@
       <c r="J417" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="K417" s="20" t="s">
+      <c r="K417" s="6" t="s">
         <v>483</v>
       </c>
     </row>
@@ -9322,7 +9302,7 @@
       <c r="J418" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="K418" s="20" t="s">
+      <c r="K418" s="6" t="s">
         <v>485</v>
       </c>
     </row>
@@ -9333,10 +9313,10 @@
       <c r="I419" s="1" t="n">
         <v>259</v>
       </c>
-      <c r="J419" s="21" t="s">
+      <c r="J419" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="K419" s="20" t="s">
+      <c r="K419" s="6" t="s">
         <v>487</v>
       </c>
     </row>
@@ -9350,7 +9330,7 @@
       <c r="J420" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="K420" s="20" t="s">
+      <c r="K420" s="6" t="s">
         <v>489</v>
       </c>
     </row>
@@ -9364,7 +9344,7 @@
       <c r="J421" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="K421" s="22" t="s">
+      <c r="K421" s="9" t="s">
         <v>491</v>
       </c>
     </row>
@@ -9378,7 +9358,7 @@
       <c r="J422" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="K422" s="20" t="s">
+      <c r="K422" s="6" t="s">
         <v>493</v>
       </c>
     </row>
@@ -9392,13 +9372,13 @@
       <c r="J423" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="K423" s="20" t="s">
+      <c r="K423" s="6" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J424" s="7"/>
-      <c r="K424" s="20"/>
+      <c r="K424" s="6"/>
     </row>
     <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E425" s="6" t="s">
@@ -9408,7 +9388,7 @@
         <v>2</v>
       </c>
       <c r="J425" s="7"/>
-      <c r="K425" s="20"/>
+      <c r="K425" s="6"/>
     </row>
     <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E426" s="1" t="s">
@@ -9418,7 +9398,7 @@
         <v>13</v>
       </c>
       <c r="J426" s="7"/>
-      <c r="K426" s="20"/>
+      <c r="K426" s="6"/>
     </row>
     <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E427" s="6" t="s">
@@ -9429,11 +9409,11 @@
       </c>
       <c r="G427" s="6"/>
       <c r="J427" s="7"/>
-      <c r="K427" s="20"/>
+      <c r="K427" s="6"/>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J428" s="18"/>
-      <c r="K428" s="20"/>
+      <c r="K428" s="6"/>
     </row>
     <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F429" s="16"/>
@@ -9446,7 +9426,7 @@
       <c r="J429" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K429" s="20" t="s">
+      <c r="K429" s="6" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9461,7 +9441,7 @@
       <c r="J430" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="K430" s="20" t="s">
+      <c r="K430" s="6" t="s">
         <v>497</v>
       </c>
     </row>
@@ -9476,7 +9456,7 @@
       <c r="J431" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="K431" s="22" t="s">
+      <c r="K431" s="9" t="s">
         <v>499</v>
       </c>
     </row>
@@ -9488,10 +9468,10 @@
       <c r="I432" s="1" t="n">
         <v>267</v>
       </c>
-      <c r="J432" s="21" t="s">
+      <c r="J432" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="K432" s="20" t="s">
+      <c r="K432" s="6" t="s">
         <v>501</v>
       </c>
     </row>
@@ -9506,7 +9486,7 @@
       <c r="J433" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K433" s="20" t="s">
+      <c r="K433" s="6" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9521,7 +9501,7 @@
       <c r="J434" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="K434" s="20" t="s">
+      <c r="K434" s="6" t="s">
         <v>503</v>
       </c>
     </row>
@@ -9533,10 +9513,10 @@
       <c r="I435" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="J435" s="21" t="s">
+      <c r="J435" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="K435" s="20" t="s">
+      <c r="K435" s="6" t="s">
         <v>505</v>
       </c>
     </row>
@@ -9548,10 +9528,10 @@
       <c r="I436" s="1" t="n">
         <v>271</v>
       </c>
-      <c r="J436" s="23" t="s">
+      <c r="J436" s="19" t="s">
         <v>506</v>
       </c>
-      <c r="K436" s="20" t="s">
+      <c r="K436" s="6" t="s">
         <v>507</v>
       </c>
     </row>
@@ -9566,7 +9546,7 @@
       <c r="J437" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="K437" s="20" t="s">
+      <c r="K437" s="6" t="s">
         <v>509</v>
       </c>
     </row>
@@ -9581,7 +9561,7 @@
       <c r="J438" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K438" s="20" t="s">
+      <c r="K438" s="6" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9593,10 +9573,10 @@
       <c r="I439" s="1" t="n">
         <v>274</v>
       </c>
-      <c r="J439" s="21" t="s">
+      <c r="J439" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="K439" s="20" t="s">
+      <c r="K439" s="6" t="s">
         <v>511</v>
       </c>
     </row>
@@ -9611,7 +9591,7 @@
       <c r="J440" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="K440" s="20" t="s">
+      <c r="K440" s="6" t="s">
         <v>513</v>
       </c>
     </row>
@@ -9626,7 +9606,7 @@
       <c r="J441" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="K441" s="20" t="s">
+      <c r="K441" s="6" t="s">
         <v>513</v>
       </c>
     </row>
@@ -9641,7 +9621,7 @@
       <c r="J442" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K442" s="20" t="s">
+      <c r="K442" s="6" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9656,7 +9636,7 @@
       <c r="J443" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="K443" s="20" t="s">
+      <c r="K443" s="6" t="s">
         <v>515</v>
       </c>
     </row>
@@ -9668,10 +9648,10 @@
       <c r="I444" s="1" t="n">
         <v>279</v>
       </c>
-      <c r="J444" s="21" t="s">
+      <c r="J444" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="K444" s="20" t="s">
+      <c r="K444" s="6" t="s">
         <v>517</v>
       </c>
     </row>
@@ -9683,10 +9663,10 @@
       <c r="I445" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="J445" s="24" t="s">
+      <c r="J445" s="19" t="s">
         <v>518</v>
       </c>
-      <c r="K445" s="20" t="s">
+      <c r="K445" s="6" t="s">
         <v>519</v>
       </c>
     </row>
@@ -9701,7 +9681,7 @@
       <c r="J446" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="K446" s="20" t="s">
+      <c r="K446" s="6" t="s">
         <v>521</v>
       </c>
     </row>
@@ -9715,7 +9695,7 @@
       <c r="J448" s="7"/>
       <c r="K448" s="6"/>
     </row>
-    <row r="449" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E449" s="1" t="s">
         <v>75</v>
       </c>

--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -299,12 +299,12 @@
 I did not share her past to speak of tragedies or the villagers' folly.</t>
   </si>
   <si>
-    <t xml:space="preserve">あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+    <t xml:space="preserve">あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+    <t xml:space="preserve">That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
   </si>
@@ -1836,7 +1836,7 @@
     <t xml:space="preserve">お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
   </si>
   <si>
     <t xml:space="preserve">A-hem... So then, #pc.

--- a/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/kettle.xlsx
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">bg_labo</t>
   </si>
   <si>
-    <t xml:space="preserve">- 古城 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Old Castle -</t>
+    <t xml:space="preserve">- 古塔 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Old Tower -</t>
   </si>
   <si>
     <t xml:space="preserve">…ソリン、君なのか？　最後に会ってから、どれほどの年月が過ぎただろう。</t>
@@ -1132,11 +1132,11 @@
   </si>
   <si>
     <t xml:space="preserve">竜の子の噂を耳にしたその日のうちには、僕は彼の居場所を見つけていました。容易いことです。僕はすぐにでも竜の子を殺し、魔石を奪うこともできた。しかし、竜の子の傍らに、あなたの姿を見とめたのです。
-そこで、この城であなたを待つことにしました。あなたなら、必ずやって来ると、わかっていたのでね。</t>
+そこで、この塔であなたを待つことにしました。あなたなら、必ずやって来ると、わかっていたのでね。</t>
   </si>
   <si>
     <t xml:space="preserve">The very day the rumor reached me, I found the whelp’s refuge. It would have been easy to kill him and take the Stone at once. But I saw you at the child’s side.
-So I chose to wait for you in this castle. I knew you would come.</t>
+So I chose to wait for you in this tower. I knew you would come.</t>
   </si>
   <si>
     <t xml:space="preserve">さあ、聞かせて下さい、師よ。あなたはあの竜の子を…竜の体にある魔石をどうするつもりですか？
@@ -1153,10 +1153,10 @@
     <t xml:space="preserve">You’re right that I cannot hand over Corgon. Before I say why, answer me this, Sorin. Are you still pursuing your research into the Magic Stone?</t>
   </si>
   <si>
-    <t xml:space="preserve">ふっ、当たり前でしょう。闇の奇形などという忌み名を持つ臭い体に魂を縛り、朽ちた古城の陰鬱な暗闇で生き続ける理由が、他にあるとでも思っているのですか？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heh. But of course. What other reason have I to bind my soul to this stinking flesh they call “dark abomination”—and linger in the gloom of a rotting old castle?</t>
+    <t xml:space="preserve">ふっ、当たり前でしょう。闇の奇形などという忌み名を持つ臭い体に魂を縛り、朽ちた古塔の陰鬱な暗闇で生き続ける理由が、他にあるとでも思っているのですか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heh. But of course. What other reason have I to bind my soul to this stinking flesh they call “dark abomination”—and linger in the gloom of a rotting old tower?</t>
   </si>
   <si>
     <t xml:space="preserve">僕は魔石の秘密を解明しなければならない。
@@ -1239,7 +1239,7 @@
   </si>
   <si>
     <t xml:space="preserve">…師よ、二百年前、僕を殺さなかったのは何故ですか？　あなたも同じ船に乗ったものと、僕は思っていたのですがね。
-まさかこの城に、二百年前あなたが果たさなかったことを、果たしに来たのですか？　もっとも、今では僕の力は遥かに強大になっています。あなたよりも、ずっとね。</t>
+まさかこの塔に、二百年前あなたが果たさなかったことを、果たしに来たのですか？　もっとも、今では僕の力は遥かに強大になっています。あなたよりも、ずっとね。</t>
   </si>
   <si>
     <t xml:space="preserve">...Master, why did you spare me two hundred years ago? I thought we sailed the same ship.
@@ -1561,11 +1561,11 @@
     <t xml:space="preserve">...Ah. It is.</t>
   </si>
   <si>
-    <t xml:space="preserve">あなたの弟子が魔石を手に入れ、その力の虜となると、あなたは弟子の居城を訪れました。弟子思いの優しいあなたは、僕の魂を救うために、僕を殺しに来たのです。
+    <t xml:space="preserve">あなたの弟子が魔石を手に入れ、その力の虜となると、あなたは弟子の居塔を訪れました。弟子思いの優しいあなたは、僕の魂を救うために、僕を殺しに来たのです。
 しかし…僕の計画を知った時、あなたの中に葛藤が生じました。</t>
   </si>
   <si>
-    <t xml:space="preserve">When your disciple gained a Magic Stone and fell captive to its power, you came to his keep. Kind, solicitous Master that you are, you came to kill me—to save my soul.
+    <t xml:space="preserve">When your disciple gained a Magic Stone and fell captive to its power, you came to his tower. Kind, solicitous Master that you are, you came to kill me—to save my soul.
 But... when you learned of my plan, a struggle took root in you.</t>
   </si>
   <si>
@@ -1645,13 +1645,13 @@
     <t xml:space="preserve">I’m glad you’re a man of understanding. It’s a simple errand.</t>
   </si>
   <si>
-    <t xml:space="preserve">この古城から少し離れた沼地に、誰も寄り付かない洞窟があります。「死者の洞窟」と呼ばれるその洞窟の奥には、死者に守られ、しかし死者が決して近づくことのできない「淀み」があるのです。
+    <t xml:space="preserve">この古塔から少し離れた沼地に、誰も寄り付かない洞窟があります。「死者の洞窟」と呼ばれるその洞窟の奥には、死者に守られ、しかし死者が決して近づくことのできない「淀み」があるのです。
 …この瓶をあなたに渡しましょう。
 あなたには、この瓶に入っている液体の雫を一滴、この「淀み」に垂らしてきてほしいのです。
 …どうです、簡単でしょう？</t>
   </si>
   <si>
-    <t xml:space="preserve">A short way from this castle, in the marsh, there is a cave shunned by all. They call it the “Crypt of the Damned.” In its depths lies a “pool of stagnation,” warded by the dead—yet one the dead themselves can never approach.
+    <t xml:space="preserve">A short way from this tower, in the marsh, there is a cave shunned by all. They call it the “Crypt of the Damned.” In its depths lies a “pool of stagnation,” warded by the dead—yet one the dead themselves can never approach.
 ...Take this vial.
 I want you to let a single drop of the liquid within fall into that pool. ...There, simple enough?</t>
   </si>
@@ -2698,11 +2698,11 @@
 Now then, Master.</t>
   </si>
   <si>
-    <t xml:space="preserve">…ソリン、その身体であの古城に帰る気かい？
+    <t xml:space="preserve">…ソリン、その身体であの古塔に帰る気かい？
 悪気はないけど、この前訪れた時は、とても「人間」がくつろげる場所だとは思えなかったよ。</t>
   </si>
   <si>
-    <t xml:space="preserve">...Sorin, are you really going back to that old castle in your...current body?
+    <t xml:space="preserve">...Sorin, are you really going back to that old tower in your...current body?
 No offense, but last time I visited your castle, it hardly felt like a place a "human" could relax.</t>
   </si>
   <si>
